--- a/artfynd/A 63859-2025 artfynd.xlsx
+++ b/artfynd/A 63859-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132901103</v>
       </c>
       <c r="B2" t="n">
-        <v>101338</v>
+        <v>101340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132901105</v>
       </c>
       <c r="B3" t="n">
-        <v>101338</v>
+        <v>101340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>132901132</v>
       </c>
       <c r="B4" t="n">
-        <v>101338</v>
+        <v>101340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>132901107</v>
       </c>
       <c r="B6" t="n">
-        <v>101338</v>
+        <v>101340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>132901133</v>
       </c>
       <c r="B7" t="n">
-        <v>96447</v>
+        <v>96449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>132901101</v>
       </c>
       <c r="B8" t="n">
-        <v>101338</v>
+        <v>101340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 63859-2025 artfynd.xlsx
+++ b/artfynd/A 63859-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132901103</v>
       </c>
       <c r="B2" t="n">
-        <v>101340</v>
+        <v>101348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132901105</v>
       </c>
       <c r="B3" t="n">
-        <v>101340</v>
+        <v>101348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>132901132</v>
       </c>
       <c r="B4" t="n">
-        <v>101340</v>
+        <v>101348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>132901107</v>
       </c>
       <c r="B6" t="n">
-        <v>101340</v>
+        <v>101348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>132901133</v>
       </c>
       <c r="B7" t="n">
-        <v>96449</v>
+        <v>96457</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>132901101</v>
       </c>
       <c r="B8" t="n">
-        <v>101340</v>
+        <v>101348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 63859-2025 artfynd.xlsx
+++ b/artfynd/A 63859-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132901133</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132901108</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132901113</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132901110</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132901102</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132901101</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132901103</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132901105</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1570,6 +1615,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132901107</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1667,6 +1717,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132901109</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1764,6 +1819,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132901132</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1861,8 +1921,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132901112</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>